--- a/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>SCBFY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,56 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -733,8 +736,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -762,8 +768,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -791,8 +800,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +816,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,8 +878,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,8 +910,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,8 +942,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,8 +955,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -959,8 +985,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,8 +1017,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,8 +1033,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,8 +1063,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1059,8 +1095,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,8 +1127,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1117,8 +1159,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1146,8 +1191,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,8 +1223,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1255,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,8 +1287,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1319,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1351,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1383,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,8 +1415,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1378,8 +1447,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1407,8 +1479,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,8 +1511,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1465,42 +1543,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1596,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,95 +1610,105 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>83422000</v>
+      </c>
+      <c r="E41" s="3">
         <v>64905000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54216000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61927000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>101460000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89137000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>114530000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>72229000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>83820000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>271595000</v>
+      </c>
+      <c r="E42" s="3">
         <v>258029000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>242151000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>222785000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>213390000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>195742000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>190910000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>176774000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>195005000</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>663000</v>
+      </c>
+      <c r="E43" s="3">
         <v>517000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>491000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>510000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>484000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>479000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>423000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>445000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1626,8 +1721,8 @@
       <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3">
-        <v>16500</v>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
@@ -1638,156 +1733,174 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6408000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1103000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6392000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>918000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6135000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5313000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10744000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7691000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6889000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>384140000</v>
+      </c>
+      <c r="E46" s="3">
         <v>327915000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>324443000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>289244000</v>
       </c>
-      <c r="G46" s="3">
-        <v>341008500</v>
-      </c>
       <c r="H46" s="3">
+        <v>340992000</v>
+      </c>
+      <c r="I46" s="3">
         <v>293660000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>337114000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>260509000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>311068900</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>145576000</v>
+      </c>
+      <c r="E47" s="3">
         <v>149184000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>153491000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>162237000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>162221000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>158064000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>163813000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>170794000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>174079000</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2425000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2283000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2202000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2252000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2274000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2159000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2216000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2289000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5522000</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5791000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6279000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6103000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6153000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6214000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5997000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5898000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5891000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +1928,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +1960,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27097000</v>
+      </c>
+      <c r="E52" s="3">
         <v>63696000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39247000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>42709000</v>
       </c>
-      <c r="G52" s="3">
-        <v>31914500</v>
-      </c>
       <c r="H52" s="3">
+        <v>31931000</v>
+      </c>
+      <c r="I52" s="3">
         <v>49133000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>39947000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57383000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32589100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2024,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>849688000</v>
+      </c>
+      <c r="E54" s="3">
         <v>872173000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>835427000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>812525000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>822844000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>825833000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>838711000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>820678000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>819922000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2072,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,182 +2086,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>513554000</v>
+      </c>
+      <c r="E57" s="3">
         <v>510312000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>518153000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>489077000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>516590000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>482901000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>515094000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>489058000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>503238000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>129255000</v>
+      </c>
+      <c r="E58" s="3">
         <v>71970000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>136736000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>60502000</v>
       </c>
-      <c r="G58" s="3">
-        <v>137659000</v>
-      </c>
       <c r="H58" s="3">
+        <v>111517000</v>
+      </c>
+      <c r="I58" s="3">
         <v>77876000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>152487000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>59552000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>156326000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52156000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1650000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>56633000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1989000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44481000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1790000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>53647000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2430000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43509000</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>701992000</v>
+      </c>
+      <c r="E60" s="3">
         <v>590564000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>718107000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>557461000</v>
       </c>
-      <c r="G60" s="3">
-        <v>705807000</v>
-      </c>
       <c r="H60" s="3">
+        <v>679665000</v>
+      </c>
+      <c r="I60" s="3">
         <v>569105000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>727546000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>556399000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>709049000</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88358000</v>
+      </c>
+      <c r="E61" s="3">
         <v>76110000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57791000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>71857000</v>
       </c>
-      <c r="G61" s="3">
-        <v>58400000</v>
-      </c>
       <c r="H61" s="3">
+        <v>84542000</v>
+      </c>
+      <c r="I61" s="3">
         <v>80565000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53145000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>164717000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51916000</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7221000</v>
+      </c>
+      <c r="E62" s="3">
         <v>151777000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7376000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>131608000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7331000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>126924000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7524000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>48676000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8026000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2308,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2340,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2372,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>798404000</v>
+      </c>
+      <c r="E66" s="3">
         <v>819437000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>784100000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>761686000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>772491000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>777477000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>789030000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>770667000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>769906000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2420,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2450,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2482,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2514,11 @@
       <c r="K70" s="3">
         <v>1494000</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>1494000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2546,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28969000</v>
+      </c>
+      <c r="E72" s="3">
         <v>28577000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29381000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28893000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28459000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27782000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28988000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28342000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28067000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2610,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2642,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2674,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49396000</v>
+      </c>
+      <c r="E76" s="3">
         <v>50845000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49423000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48940000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48463000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46484000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47821000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48143000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48172000</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,42 +2738,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +2807,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,8 +2823,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2655,8 +2853,11 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +2885,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +2917,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +2949,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +2981,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,8 +3013,11 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -2829,8 +3045,11 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,8 +3061,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2871,8 +3091,11 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3123,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,8 +3155,11 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -2958,8 +3187,11 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,8 +3203,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3000,8 +3233,11 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3265,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3297,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,8 +3329,11 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3116,8 +3361,11 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3145,8 +3393,11 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3172,6 +3423,9 @@
         <v>4</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>SCBFY</t>
   </si>
@@ -656,59 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,8 +777,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +812,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,8 +897,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -913,8 +932,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,8 +967,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,8 +981,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -988,8 +1014,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,8 +1049,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,8 +1066,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1099,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1098,8 +1134,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,8 +1169,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,8 +1204,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1239,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,8 +1274,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1258,8 +1309,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1290,8 +1344,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,8 +1484,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1519,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1482,8 +1554,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,8 +1589,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1546,45 +1624,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,112 +1696,122 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70425000</v>
+      </c>
+      <c r="E41" s="3">
         <v>83422000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>64905000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>54216000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61927000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>101460000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89137000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>114530000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>72229000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>83820000</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>262745000</v>
+      </c>
+      <c r="E42" s="3">
         <v>271595000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>258029000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>242151000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>222785000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>213390000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>195742000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>190910000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>176774000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>195005000</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E43" s="3">
         <v>663000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>517000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>491000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>510000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>484000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>479000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>423000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>445000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
+      <c r="E44" s="3">
+        <v>23700</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>4</v>
@@ -1727,8 +1822,8 @@
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
+      <c r="I44" s="3">
+        <v>16500</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
@@ -1736,171 +1831,189 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>733000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6408000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1103000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6392000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>918000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6135000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5313000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10744000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7691000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6889000</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>384140000</v>
+        <v>337527000</v>
       </c>
       <c r="E46" s="3">
+        <v>384163700</v>
+      </c>
+      <c r="F46" s="3">
         <v>327915000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>324443000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>289244000</v>
       </c>
-      <c r="H46" s="3">
-        <v>340992000</v>
-      </c>
       <c r="I46" s="3">
+        <v>341008500</v>
+      </c>
+      <c r="J46" s="3">
         <v>293660000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>337114000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>260509000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>311068900</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>152723000</v>
+      </c>
+      <c r="E47" s="3">
         <v>145576000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>149184000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>153491000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>162237000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>162221000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>158064000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>163813000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>170794000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>174079000</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2396000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2425000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2283000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2202000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2252000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2274000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2159000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2216000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2289000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5522000</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5838000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5791000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6279000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6103000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6153000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6214000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5997000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5898000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5891000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27097000</v>
+        <v>58462000</v>
       </c>
       <c r="E52" s="3">
+        <v>27073300</v>
+      </c>
+      <c r="F52" s="3">
         <v>63696000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39247000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42709000</v>
       </c>
-      <c r="H52" s="3">
-        <v>31931000</v>
-      </c>
       <c r="I52" s="3">
+        <v>31914500</v>
+      </c>
+      <c r="J52" s="3">
         <v>49133000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39947000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57383000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32589100</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>874446000</v>
+      </c>
+      <c r="E54" s="3">
         <v>849688000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>872173000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>835427000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>812525000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>822844000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>825833000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>838711000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>820678000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>819922000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,200 +2216,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>519490000</v>
+      </c>
+      <c r="E57" s="3">
         <v>513554000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>510312000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>518153000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>489077000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>516590000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>482901000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>515094000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>489058000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>503238000</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>129255000</v>
+        <v>66768000</v>
       </c>
       <c r="E58" s="3">
+        <v>159293000</v>
+      </c>
+      <c r="F58" s="3">
         <v>71970000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>136736000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>60502000</v>
       </c>
-      <c r="H58" s="3">
-        <v>111517000</v>
-      </c>
       <c r="I58" s="3">
+        <v>137659000</v>
+      </c>
+      <c r="J58" s="3">
         <v>77876000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>152487000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59552000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>156326000</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1305000</v>
+      </c>
+      <c r="E59" s="3">
         <v>52156000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1650000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56633000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1989000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44481000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1790000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>53647000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2430000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43509000</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>701992000</v>
+        <v>593342000</v>
       </c>
       <c r="E60" s="3">
+        <v>732030000</v>
+      </c>
+      <c r="F60" s="3">
         <v>590564000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>718107000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>557461000</v>
       </c>
-      <c r="H60" s="3">
-        <v>679665000</v>
-      </c>
       <c r="I60" s="3">
+        <v>705807000</v>
+      </c>
+      <c r="J60" s="3">
         <v>569105000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>727546000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>556399000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>709049000</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>88358000</v>
+        <v>79503000</v>
       </c>
       <c r="E61" s="3">
+        <v>58320000</v>
+      </c>
+      <c r="F61" s="3">
         <v>76110000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57791000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>71857000</v>
       </c>
-      <c r="H61" s="3">
-        <v>84542000</v>
-      </c>
       <c r="I61" s="3">
+        <v>58400000</v>
+      </c>
+      <c r="J61" s="3">
         <v>80565000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53145000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164717000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51916000</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>148238000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7221000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>151777000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7376000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>131608000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7331000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>126924000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7524000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>48676000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8026000</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>821978000</v>
+      </c>
+      <c r="E66" s="3">
         <v>798404000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>819437000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>784100000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>761686000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>772491000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>777477000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>789030000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>770667000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>769906000</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>1494000</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>1494000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28808000</v>
+      </c>
+      <c r="E72" s="3">
         <v>28969000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28577000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29381000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28893000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28459000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27782000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28988000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28342000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28067000</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50565000</v>
+      </c>
+      <c r="E76" s="3">
         <v>49396000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50845000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49423000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48940000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48463000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46484000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47821000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48143000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48172000</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,45 +2929,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2810,8 +3004,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,8 +3021,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2856,8 +3054,11 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,8 +3229,11 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3048,8 +3264,11 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,8 +3281,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3094,8 +3314,11 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,8 +3384,11 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3190,8 +3419,11 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,8 +3436,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3236,8 +3469,11 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,8 +3574,11 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3364,8 +3609,11 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3396,8 +3644,11 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3426,6 +3677,9 @@
         <v>4</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>SCBFY</t>
   </si>
@@ -656,62 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +748,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,8 +786,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -815,8 +824,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +842,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +878,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,8 +916,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -935,8 +954,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -970,8 +992,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,8 +1007,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1017,8 +1043,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1052,8 +1081,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,8 +1099,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1102,8 +1135,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1137,8 +1173,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1172,8 +1211,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1207,8 +1249,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1242,8 +1287,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,8 +1325,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1312,8 +1363,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1347,8 +1401,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,8 +1439,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1417,8 +1477,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1515,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,8 +1553,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1522,8 +1591,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1557,8 +1629,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,8 +1667,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1627,48 +1705,54 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1766,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,323 +1782,351 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>96246000</v>
+      </c>
+      <c r="E41" s="3">
         <v>70425000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>83422000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>64905000</v>
       </c>
-      <c r="G41" s="3">
-        <v>54216000</v>
-      </c>
       <c r="H41" s="3">
+        <v>87518000</v>
+      </c>
+      <c r="I41" s="3">
         <v>61927000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>101460000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89137000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>114530000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72229000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>83820000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>274187000</v>
+      </c>
+      <c r="E42" s="3">
         <v>262745000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>271595000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>258029000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>242151000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>222785000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>213390000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>195742000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>190910000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>176774000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>195005000</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>572000</v>
+      </c>
+      <c r="E43" s="3">
         <v>602000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>663000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>517000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>491000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>510000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>484000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>479000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>423000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>445000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>23700</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>16500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5602000</v>
+      </c>
+      <c r="E45" s="3">
         <v>733000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6408000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1103000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6392000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>918000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6135000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5313000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10744000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7691000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6889000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>404484000</v>
+      </c>
+      <c r="E46" s="3">
         <v>337527000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>384163700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>327915000</v>
       </c>
-      <c r="G46" s="3">
-        <v>324443000</v>
-      </c>
       <c r="H46" s="3">
+        <v>357745000</v>
+      </c>
+      <c r="I46" s="3">
         <v>289244000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>341008500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>293660000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>337114000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>260509000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>311068900</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>156965000</v>
+      </c>
+      <c r="E47" s="3">
         <v>152723000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>145576000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>149184000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>153491000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>162237000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>162221000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>158064000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>163813000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>170794000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>174079000</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2506000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2396000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2425000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2283000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2202000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2252000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2274000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2159000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2216000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2289000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5522000</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6091000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5838000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5791000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6279000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6103000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6153000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6214000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5997000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5898000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5891000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2160,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2198,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46778000</v>
+      </c>
+      <c r="E52" s="3">
         <v>58462000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27073300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63696000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39247000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42709000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31914500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>49133000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39947000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57383000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32589100</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2274,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>913936000</v>
+      </c>
+      <c r="E54" s="3">
         <v>874446000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>849688000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>872173000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>835427000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>812525000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>822844000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>825833000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>838711000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>820678000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>819922000</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2330,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,218 +2346,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>575225000</v>
+      </c>
+      <c r="E57" s="3">
         <v>519490000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>513554000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>510312000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>518153000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>489077000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>516590000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>482901000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>515094000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>489058000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>503238000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>152231000</v>
+      </c>
+      <c r="E58" s="3">
         <v>66768000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>159293000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>71970000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>136736000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>60502000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>137659000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>77876000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>152487000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59552000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>156326000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56985000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1305000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52156000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1650000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56633000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1989000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44481000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1790000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>53647000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2430000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>43509000</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>790883000</v>
+      </c>
+      <c r="E60" s="3">
         <v>593342000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>732030000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>590564000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>718107000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>557461000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>705807000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>569105000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>727546000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>556399000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>709049000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>59905000</v>
+      </c>
+      <c r="E61" s="3">
         <v>79503000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58320000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>76110000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>57791000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>71857000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58400000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>80565000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53145000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>164717000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51916000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7481000</v>
+      </c>
+      <c r="E62" s="3">
         <v>148238000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7221000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>151777000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7376000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>131608000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7331000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>126924000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7524000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48676000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8026000</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2610,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2648,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2686,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>859266000</v>
+      </c>
+      <c r="E66" s="3">
         <v>821978000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>798404000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>819437000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>784100000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>761686000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>772491000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>777477000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>789030000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>770667000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>769906000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2742,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2778,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2816,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +2854,11 @@
       <c r="M70" s="3">
         <v>1494000</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>1494000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +2892,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29983000</v>
+      </c>
+      <c r="E72" s="3">
         <v>28808000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28969000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28577000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29381000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28893000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28459000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27782000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28988000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28342000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28067000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +2968,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3006,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3044,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52736000</v>
+      </c>
+      <c r="E76" s="3">
         <v>50565000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49396000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50845000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49423000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48940000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>48463000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46484000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47821000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48143000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48172000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,48 +3120,54 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3007,8 +3201,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,8 +3219,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3057,8 +3255,11 @@
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3293,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3331,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3369,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3407,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,8 +3445,11 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3267,8 +3483,11 @@
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,8 +3501,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3317,8 +3537,11 @@
       <c r="M91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3575,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,8 +3613,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3422,8 +3651,11 @@
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,8 +3669,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3472,8 +3705,11 @@
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3743,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +3781,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,8 +3819,11 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3612,8 +3857,11 @@
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3647,8 +3895,11 @@
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3680,6 +3931,9 @@
         <v>4</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="92">
   <si>
     <t>SCBFY</t>
   </si>
@@ -656,68 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +760,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +804,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +848,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +868,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +910,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +954,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +998,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1042,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1059,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1101,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1145,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1165,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1207,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1251,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1295,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1339,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1383,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1427,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1471,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1515,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1559,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1603,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1647,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1691,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1735,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1779,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1823,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1867,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +1936,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,131 +1954,141 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88424000</v>
+      </c>
+      <c r="E41" s="3">
         <v>86800000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>96246000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>70425000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83422000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64905000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>87518000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61927000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101460000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>89137000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>114530000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72229000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>83820000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>273006000</v>
+      </c>
+      <c r="E42" s="3">
         <v>262449000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>274187000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>262745000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>271595000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>258029000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>242151000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>222785000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>213390000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>195742000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>190910000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>176774000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>195005000</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E43" s="3">
         <v>571000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>572000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>602000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>663000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>517000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>491000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>510000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>484000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>479000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>423000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>445000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2006,8 +2101,8 @@
       <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3">
-        <v>23700</v>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
@@ -2018,228 +2113,246 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>16500</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7660000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1855000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5602000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>733000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6408000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1103000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6392000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>918000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6135000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5313000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10744000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7691000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6889000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>397220000</v>
+      </c>
+      <c r="E46" s="3">
         <v>354800000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>404484000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>337527000</v>
       </c>
-      <c r="G46" s="3">
-        <v>384163700</v>
-      </c>
       <c r="H46" s="3">
+        <v>384140000</v>
+      </c>
+      <c r="I46" s="3">
         <v>327915000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>357745000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>289244000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>341008500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>293660000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>337114000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>260509000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>311068900</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>168382000</v>
+      </c>
+      <c r="E47" s="3">
         <v>163777000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>156965000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>152723000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>145576000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>149184000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>153491000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>162237000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>162221000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>158064000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>163813000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>170794000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>174079000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2559000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2477000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2506000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2396000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2425000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2283000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2202000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2252000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2274000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2159000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2216000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2289000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5522000</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6231000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6145000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6091000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5838000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5791000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6279000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6103000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6153000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6214000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5997000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5898000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5891000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2392,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2436,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48656000</v>
+      </c>
+      <c r="E52" s="3">
         <v>65290000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>46778000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58462000</v>
       </c>
-      <c r="G52" s="3">
-        <v>27073300</v>
-      </c>
       <c r="H52" s="3">
+        <v>27097000</v>
+      </c>
+      <c r="I52" s="3">
         <v>63696000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>39247000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42709000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31914500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>49133000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39947000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>57383000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32589100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2524,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>919955000</v>
+      </c>
+      <c r="E54" s="3">
         <v>913650000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>913936000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>874446000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>849688000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>872173000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>835427000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>812525000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>822844000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>825833000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>838711000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>820678000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>819922000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2588,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2606,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>582749000</v>
+      </c>
+      <c r="E57" s="3">
         <v>556287000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>575225000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>519490000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>513554000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>510312000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>518153000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>489077000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>516590000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>482901000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>515094000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>489058000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>503238000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>146344000</v>
+      </c>
+      <c r="E58" s="3">
         <v>63997000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152231000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66768000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>159293000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>71970000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>136736000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>60502000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>137659000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>77876000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>152487000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>59552000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>156326000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>55284000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1949000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>56985000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1305000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52156000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1650000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>56633000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1989000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44481000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1790000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>53647000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2430000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43509000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>791982000</v>
+      </c>
+      <c r="E60" s="3">
         <v>628793000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>790883000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>593342000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>732030000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>590564000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>718107000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>557461000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>705807000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>569105000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>727546000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>556399000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>709049000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>64843000</v>
+      </c>
+      <c r="E61" s="3">
         <v>84026000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>59905000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79503000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>58320000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>76110000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>57791000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>71857000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58400000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>80565000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>53145000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>164717000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51916000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7469000</v>
+      </c>
+      <c r="E62" s="3">
         <v>146596000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7481000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>148238000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7221000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>151777000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7376000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>131608000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7331000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>126924000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7524000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>48676000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8026000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +2912,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +2956,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3000,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>865369000</v>
+      </c>
+      <c r="E66" s="3">
         <v>860430000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>859266000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>821978000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>798404000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>819437000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>784100000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>761686000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>772491000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>777477000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>789030000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>770667000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>769906000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3064,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3106,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3150,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3194,11 @@
       <c r="O70" s="3">
         <v>1494000</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>1494000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3238,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29573000</v>
+      </c>
+      <c r="E72" s="3">
         <v>29441000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29983000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28808000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28969000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28577000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29381000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28893000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28459000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27782000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28988000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28342000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28067000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3326,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3370,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3414,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52627000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51291000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52736000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50565000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49396000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50845000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49423000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48940000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48463000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46484000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47821000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48143000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48172000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3502,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3595,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,8 +3615,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3459,8 +3657,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3701,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3745,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3789,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +3833,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,8 +3877,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3705,8 +3921,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,8 +3941,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3763,8 +3983,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4027,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,8 +4071,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3886,8 +4115,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,8 +4135,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3944,8 +4177,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4221,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4265,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,8 +4309,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4108,8 +4353,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4149,8 +4397,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4188,6 +4439,9 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="92">
   <si>
     <t>SCBFY</t>
   </si>
@@ -656,71 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +766,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +813,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +860,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +881,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +926,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +973,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1020,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,8 +1067,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1085,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1104,8 +1130,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,8 +1177,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1198,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1243,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1254,8 +1290,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1337,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1384,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,8 +1431,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1478,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1474,8 +1525,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1518,8 +1572,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1619,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1666,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1713,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1760,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1738,8 +1807,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1782,8 +1854,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1901,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1870,57 +1948,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2021,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,140 +2040,150 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71247000</v>
+      </c>
+      <c r="E41" s="3">
         <v>88424000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>86800000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>96246000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>70425000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83422000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64905000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>87518000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>61927000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101460000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89137000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>114530000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>72229000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>83820000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>315420000</v>
+      </c>
+      <c r="E42" s="3">
         <v>273006000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>262449000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>274187000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>262745000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>271595000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>258029000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>242151000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>222785000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>213390000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>195742000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>190910000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>176774000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>195005000</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E43" s="3">
         <v>574000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>571000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>572000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>602000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>663000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>517000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>491000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>510000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>484000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>479000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>423000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>445000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2116,243 +2211,261 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>16500</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>807000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7660000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1855000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5602000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>733000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6408000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1103000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6392000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>918000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6135000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5313000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10744000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7691000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6889000</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>390883000</v>
+      </c>
+      <c r="E46" s="3">
         <v>397220000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>354800000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>404484000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>337527000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>384140000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>327915000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>357745000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>289244000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>341008500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>293660000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>337114000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>260509000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>311068900</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>160551000</v>
+      </c>
+      <c r="E47" s="3">
         <v>168382000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>163777000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>156965000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>152723000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>145576000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>149184000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>153491000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>162237000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>162221000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>158064000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>163813000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>170794000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>174079000</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2427000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2559000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2477000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2506000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2396000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2425000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2283000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2202000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2252000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2274000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2159000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2216000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2289000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5522000</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6268000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6231000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6145000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6091000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5838000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5791000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6279000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6103000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6153000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6214000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5997000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5898000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5891000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5869000</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2508,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2555,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>82852000</v>
+      </c>
+      <c r="E52" s="3">
         <v>48656000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>65290000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>46778000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>58462000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27097000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63696000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39247000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42709000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31914500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>49133000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39947000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>57383000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32589100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2649,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>972907000</v>
+      </c>
+      <c r="E54" s="3">
         <v>919955000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>913650000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>913936000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>874446000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>849688000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>872173000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>835427000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>812525000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>822844000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>825833000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>838711000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>820678000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>819922000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2717,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,272 +2736,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>571042000</v>
+      </c>
+      <c r="E57" s="3">
         <v>582749000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>556287000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>575225000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>519490000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>513554000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>510312000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>518153000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>489077000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>516590000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>482901000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>515094000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>489058000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>503238000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>104866000</v>
+      </c>
+      <c r="E58" s="3">
         <v>146344000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>63997000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>152231000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>66768000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>159293000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>71970000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>136736000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>60502000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>137659000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>77876000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>152487000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>59552000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>156326000</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1553000</v>
+      </c>
+      <c r="E59" s="3">
         <v>55284000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1949000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56985000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1305000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52156000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1650000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56633000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1989000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44481000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1790000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>53647000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2430000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43509000</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>683018000</v>
+      </c>
+      <c r="E60" s="3">
         <v>791982000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>628793000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>790883000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>593342000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>732030000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>590564000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>718107000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>557461000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>705807000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>569105000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>727546000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>556399000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>709049000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>84491000</v>
+      </c>
+      <c r="E61" s="3">
         <v>64843000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>84026000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>59905000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>79503000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>58320000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>76110000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57791000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>71857000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>58400000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>80565000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53145000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>164717000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51916000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>149635000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7469000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>146596000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7481000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>148238000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7221000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>151777000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7376000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>131608000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7331000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>126924000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7524000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48676000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8026000</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3063,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3110,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3157,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>918222000</v>
+      </c>
+      <c r="E66" s="3">
         <v>865369000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>860430000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>859266000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>821978000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>798404000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>819437000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>784100000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>761686000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>772491000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>777477000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>789030000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>770667000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>769906000</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3225,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3270,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3317,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3364,11 @@
       <c r="P70" s="3">
         <v>1494000</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>1494000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3411,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29528000</v>
+      </c>
+      <c r="E72" s="3">
         <v>29573000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29441000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29983000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28808000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28969000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28577000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29381000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28893000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28459000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27782000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28988000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28342000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>28067000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3505,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3552,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3599,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52712000</v>
+      </c>
+      <c r="E76" s="3">
         <v>52627000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51291000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>52736000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50565000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49396000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50845000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49423000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48940000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48463000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46484000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47821000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48143000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48172000</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3693,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3598,8 +3792,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,8 +3813,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3660,8 +3858,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +3905,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +3952,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +3999,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4046,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,8 +4093,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3924,8 +4140,11 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,8 +4161,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3986,8 +4206,11 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4253,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,8 +4300,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4118,8 +4347,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,8 +4368,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4180,8 +4413,11 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4460,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4507,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,8 +4554,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4356,8 +4601,11 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4400,8 +4648,11 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4442,6 +4693,9 @@
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
